--- a/FINAL_SUBMISSION/19_决策后验证/19_决策后验证.xlsx
+++ b/FINAL_SUBMISSION/19_决策后验证/19_决策后验证.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>27.87</v>
+        <v>27.839</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>13500</v>
@@ -1103,6 +1103,87 @@
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>D20260909M01</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业(601899)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>18200</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>待观察</t>
         </is>
@@ -1146,7 +1227,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1238,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -1177,7 +1258,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
